--- a/results/Int Task Remove ACC 0.6/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.6/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0002686294864849938</v>
+        <v>-0.0006040429671685464</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.005344639046236126</v>
+        <v>-0.001342968565665299</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.003904421157285079</v>
+        <v>-0.002163640604601207</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0006499369603295989</v>
+        <v>-0.0001991109589638362</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.004361180418365012</v>
+        <v>-0.003023108399995408</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0002000699668989602</v>
+        <v>0.0003318228110348068</v>
       </c>
       <c r="I3" t="n">
-        <v>5.951296181712306e-05</v>
+        <v>6.399304630873348e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001149544044352499</v>
+        <v>-0.001840972870498715</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007112868123044386</v>
+        <v>0.009810157815465865</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003616356308137025</v>
+        <v>0.01085963582588921</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0009501551121017115</v>
+        <v>0.001781605034232467</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.002544549836524719</v>
+        <v>0.0003818653007012561</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.003482750775232372</v>
+        <v>-0.0006880491612900421</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004810825771601412</v>
+        <v>0.004306131359457846</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01077686749925573</v>
+        <v>0.01319801471213848</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001914550902343447</v>
+        <v>-0.00133932940061806</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0007909623555018187</v>
+        <v>-7.913128024179491e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009317472377830184</v>
+        <v>0.001801059760884639</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001307454010424142</v>
+        <v>1.387559707391949e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001025276710698775</v>
+        <v>0.0002707481581379445</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0008288356595647286</v>
+        <v>0.00167351958442804</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001790785399162575</v>
+        <v>-0.002941019899300666</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001402173087491287</v>
+        <v>0.0001484126674059005</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0002552160564958339</v>
+        <v>-0.000543065606565991</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001516240376473776</v>
+        <v>0.0008592813325817373</v>
       </c>
       <c r="AB3" t="n">
-        <v>-7.962447306942067e-05</v>
+        <v>-0.0001995022071830588</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.002201809267137885</v>
+        <v>0.0003941523989755082</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.0009168055278797485</v>
+        <v>-0.003315103305702073</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0005625410467109993</v>
+        <v>-0.002089099165500343</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.002408883049623067</v>
+        <v>-0.005486804104807989</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0001334814674880924</v>
+        <v>-0.00031631281682723</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0001991780716396873</v>
+        <v>-6.361194474982179e-05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.0004439086772498869</v>
+        <v>-0.001075985820611542</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.000774219290434828</v>
+        <v>-0.001467847871696017</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0002110886250102684</v>
+        <v>-0.0001374793574056188</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0002584453001802123</v>
+        <v>0.0001429407455082387</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001447688067678934</v>
+        <v>0.0003698016417179107</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001009959846331031</v>
+        <v>-0.0007735318579217209</v>
       </c>
       <c r="AP3" t="n">
-        <v>-9.172889180394275e-05</v>
+        <v>-0.0002115362217525862</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001131782016970963</v>
+        <v>0.001263137236586314</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0008175800442498195</v>
+        <v>-0.0005136880178207437</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0009768531141672043</v>
+        <v>-0.0004344754229658432</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.002220183296261251</v>
+        <v>-0.003198727066111994</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.005217110013394446</v>
+        <v>-0.005506359395698928</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0005759981084627342</v>
+        <v>0.0002206270316984116</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.001252400485862459</v>
+        <v>-0.001706873857972347</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0003808348568117248</v>
+        <v>-0.000132049370470535</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0004634785991690906</v>
+        <v>-0.00112921323346263</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.003822876725030096</v>
+        <v>-0.001381549154142301</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.0009441235082686461</v>
+        <v>-0.003632549793856675</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.001811460035530157</v>
+        <v>-0.003148164322610578</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0002699781342506846</v>
+        <v>-0.0003211789915891594</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0002912477460388041</v>
+        <v>-0.0001488627966893863</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.002233473121052256</v>
+        <v>-0.00104210833308047</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.003859129349374143</v>
+        <v>-0.002881919976271215</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.003399805936046441</v>
+        <v>-0.003121913311357018</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.0003526694982003198</v>
+        <v>-0.0002322618285867617</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.0009250284452942481</v>
+        <v>-0.0001742117385356403</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.005135731464992269</v>
+        <v>-0.005678467142497601</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0006023873573681694</v>
+        <v>5.567700668311913e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.000359146942631202</v>
+        <v>0.0007853155095378459</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.005864941131657465</v>
+        <v>-0.002697096805617647</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.003054796021736487</v>
+        <v>-0.002113273176695614</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.001884991582571692</v>
+        <v>0.0002423958167884668</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.370079775324558e-06</v>
+        <v>-2.570633646730936e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.0003509566643116957</v>
+        <v>-0.0002392261691397124</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0002795081332964533</v>
+        <v>-0.0009048404625621043</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0002530423318843367</v>
+        <v>0.0002540297529127689</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.000546026704468111</v>
+        <v>-0.002179304343149973</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.00109318274169229</v>
+        <v>0.001275762691841438</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.002539396506762814</v>
+        <v>-0.0009402945730324231</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0001779327692434229</v>
+        <v>-4.299797426276619e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.276469925257099e-05</v>
+        <v>0.0002236291306298998</v>
       </c>
       <c r="BZ3" t="n">
-        <v>6.664465833636118e-05</v>
+        <v>-0.000234046577888416</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.086336706388802e-05</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0002288252440912742</v>
+        <v>3.914480183198234e-07</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0008389741225326833</v>
+        <v>-0.000535456170027545</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.20206967046588e-05</v>
+        <v>-0.0003184327492904237</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0003664670394201963</v>
+        <v>-0.0001185181182584028</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0007768149771067068</v>
+        <v>-0.0003147023878103116</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.001593784078386326</v>
+        <v>-0.0001942556282398466</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0002970203586105357</v>
+        <v>-0.000348460899802071</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.001791184168210387</v>
+        <v>0.0005017312266017537</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.00138864392439376</v>
+        <v>0.0007972192787369381</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0008976553271164767</v>
+        <v>0.001202295850693275</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009049337307813024</v>
+        <v>0.007684086537059172</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01716240770484572</v>
+        <v>0.009282178522995656</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0129660643700045</v>
+        <v>0.006503260127987884</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005095659541510454</v>
+        <v>0.003566786379857306</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01441014591700218</v>
+        <v>0.007162171309707862</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002736653124381453</v>
+        <v>0.005872607525591866</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004139666774599865</v>
+        <v>0.0003078036926960262</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007596713881956741</v>
+        <v>0.007558020896389583</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01738429082380593</v>
+        <v>0.02635361160222508</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01479645432685435</v>
+        <v>0.02762136587701544</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004867580158205809</v>
+        <v>0.0026129274177267</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01278063917172228</v>
+        <v>0.007590362628569821</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01616832350772494</v>
+        <v>0.006277930764088346</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01232243200324498</v>
+        <v>0.01374280925205598</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0142263048580537</v>
+        <v>0.01420446882516196</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003854911908125628</v>
+        <v>0.009232840389883879</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008900987445971242</v>
+        <v>0.006905763038359532</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00707688730270723</v>
+        <v>0.005134201603785473</v>
       </c>
       <c r="U4" t="n">
-        <v>0.009368113870014939</v>
+        <v>0.008849715812197163</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00057167230018296</v>
+        <v>0.0006245631359165511</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005855123370615294</v>
+        <v>0.004949701200948279</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005218704474496095</v>
+        <v>0.005445451271791929</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003166629851564141</v>
+        <v>0.001963422615195209</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001767617095993708</v>
+        <v>0.002112532399623225</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002901426707686457</v>
+        <v>0.002137855462071219</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0004623739288646272</v>
+        <v>0.0007624775694078031</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.006388876146299094</v>
+        <v>0.004423500335908177</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.006170777323811176</v>
+        <v>0.006649017676623081</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.003642714986867572</v>
+        <v>0.006296260679993951</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005408368772719528</v>
+        <v>0.008160144077208354</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0005046327148670118</v>
+        <v>0.0008078583830466431</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001288360329672841</v>
+        <v>0.0007573294501629334</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005628007674238126</v>
+        <v>0.003231152033509567</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.007453513194022921</v>
+        <v>0.004749748634726541</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001047443368960754</v>
+        <v>0.0004728584466034777</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0007947586705021502</v>
+        <v>0.001336655732520844</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.003674705685130844</v>
+        <v>0.001682386893443261</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.005425000521722645</v>
+        <v>0.005140141287990826</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001676385144024051</v>
+        <v>0.0008505311226695686</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003154024034221589</v>
+        <v>0.003975489615389005</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.002077222280545952</v>
+        <v>0.00358467077420807</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.003628248452136451</v>
+        <v>0.003074242458726339</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.01121201445172917</v>
+        <v>0.007368857549241816</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.006224595814914808</v>
+        <v>0.0081133076677312</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.005523604042973474</v>
+        <v>0.00355631655702223</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.007835390248719045</v>
+        <v>0.006119350297506583</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0005068331918702879</v>
+        <v>0.0005155677086874066</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.004504047694201843</v>
+        <v>0.005336628258105017</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.005825267627251282</v>
+        <v>0.006938125428981288</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.006725491270742794</v>
+        <v>0.01324650668507036</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01356343979268052</v>
+        <v>0.008876618669157024</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0005445108531987716</v>
+        <v>0.0008252058994713565</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.000795846058115233</v>
+        <v>0.0004559230484354226</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.006469030048951414</v>
+        <v>0.003575848479292238</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.010505635437276</v>
+        <v>0.01004282104960457</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.005932122631134499</v>
+        <v>0.009011188357468863</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0007305801807144292</v>
+        <v>0.001222498549153999</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.005380574155421056</v>
+        <v>0.005329129798937239</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.01068120832695307</v>
+        <v>0.01577586071516686</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001114210065925076</v>
+        <v>0.0007801735930338198</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.006993243023939088</v>
+        <v>0.007157884348221191</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.008429179871372408</v>
+        <v>0.01101217535065197</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.009379069976705443</v>
+        <v>0.006986289492958478</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.004158688355613622</v>
+        <v>0.01022496416834082</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0001445404425272406</v>
+        <v>4.400782617904708e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.003972067775354696</v>
+        <v>0.004831159863054945</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003559562409805333</v>
+        <v>0.002865558846572016</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001408166075085008</v>
+        <v>0.002248640917461415</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.002973583026139183</v>
+        <v>0.006124867145973716</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003816242966378693</v>
+        <v>0.005117191367259197</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.008134200115919915</v>
+        <v>0.00456411143122186</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0002452274310530747</v>
+        <v>0.0001213540103709765</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0009200810024441605</v>
+        <v>0.0006422995440179621</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001704657005558395</v>
+        <v>0.0007099528388398783</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0001995990899432704</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0008703052803652521</v>
+        <v>0.001287410455355034</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.006023336629058033</v>
+        <v>0.005310421855031993</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0001160115460354888</v>
+        <v>0.0007853982044698501</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0008060137621577921</v>
+        <v>0.001882482409367199</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002688377862373866</v>
+        <v>0.00742638115396614</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004176923932513726</v>
+        <v>0.004178761581074647</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001172647066975977</v>
+        <v>0.0007669733002572287</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.004003874385483074</v>
+        <v>0.003473017403999703</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.005098292529330689</v>
+        <v>0.00567162865066821</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.003163283168600859</v>
+        <v>0.003744475843896663</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.02235108065366374</v>
+        <v>-0.02029520295202949</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.04976278334211919</v>
+        <v>-0.02135493372606778</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03769109119662628</v>
+        <v>-0.02013705851344224</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.008836310960888405</v>
+        <v>-0.008981168517624327</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.04438587243015289</v>
+        <v>-0.01813389562467053</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.00500736377025035</v>
+        <v>-0.0128008192524321</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0008434370057986418</v>
+        <v>-0.0003072196620583556</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01419604056011584</v>
+        <v>-0.01582181259600609</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03103112840466928</v>
+        <v>-0.04571984435797671</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.02850194552529185</v>
+        <v>-0.04640077821011679</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.009970817120622644</v>
+        <v>-0.003141875306823805</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.03832366895097524</v>
+        <v>-0.01765946230890881</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.04802319451765952</v>
+        <v>-0.01665788086452295</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01739588824459678</v>
+        <v>-0.01908276225619396</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.007801792303637334</v>
+        <v>-0.002252944188428019</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.004813108038914449</v>
+        <v>-0.02293906810035838</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.02329994728518716</v>
+        <v>-0.01333684765419084</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.008215593929879694</v>
+        <v>-0.005535055350553475</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.01892461781760681</v>
+        <v>-0.01481286241433842</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0008961518186610728</v>
+        <v>-0.00014333492594365</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0115972588297312</v>
+        <v>-0.003426462836056898</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01081603090294541</v>
+        <v>-0.0138147566718995</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.002897838899803518</v>
+        <v>-0.002388915432393746</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.004270986745213534</v>
+        <v>-0.003258754863813229</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.002946954813359515</v>
+        <v>-0.002577821011673143</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.000889586603872361</v>
+        <v>-0.001331285202252874</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.01261213720316624</v>
+        <v>-0.005058939096267201</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01072736787022507</v>
+        <v>-0.01407639979068547</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.005218766473379055</v>
+        <v>-0.01472754050073644</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0168498168498169</v>
+        <v>-0.01899529042386184</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0009727626459144045</v>
+        <v>-0.00150778210116731</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.003436426116838476</v>
+        <v>-0.001433349259436278</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.007484307098020249</v>
+        <v>-0.005890873973925648</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.008112023177209026</v>
+        <v>-0.01292517006802719</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002611367127496112</v>
+        <v>-0.001129666011787844</v>
       </c>
       <c r="AM5" t="n">
+        <v>-0.002111984282907686</v>
+      </c>
+      <c r="AN5" t="n">
         <v>-0.001620029455080996</v>
       </c>
-      <c r="AN5" t="n">
-        <v>-0.002796833773087093</v>
-      </c>
       <c r="AO5" t="n">
-        <v>-0.005697730564944437</v>
+        <v>-0.01154031868662481</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.003387334315169355</v>
+        <v>-0.001556420233463029</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.002216358839050159</v>
+        <v>-0.004766536964980572</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.003730976926853202</v>
+        <v>-0.007774022211492015</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.00622691292875992</v>
+        <v>-0.005273937532002016</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.02601583113456465</v>
+        <v>-0.01735791090629797</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.01523458091723779</v>
+        <v>-0.01493123772102165</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.01308215593929886</v>
+        <v>-0.006041257367387054</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01329147043432763</v>
+        <v>-0.01166928309785449</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001424802110817991</v>
+        <v>-0.000917431192660556</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.009262166405023609</v>
+        <v>-0.0110087045570916</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.01202749140893467</v>
+        <v>-0.01303501945525298</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01571011673151756</v>
+        <v>-0.0333171206225681</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01658560311284052</v>
+        <v>-0.01429961089494169</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0004418262150220897</v>
+        <v>-0.001352003862868201</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0008122312470139281</v>
+        <v>-0.0009728622631847928</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.01889182058047495</v>
+        <v>-0.01018945212493595</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.02402723735408563</v>
+        <v>-0.02091439688715957</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01602662570404501</v>
+        <v>-0.02305447470817124</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001914580265095722</v>
+        <v>-0.002356406480117823</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.01219256933542654</v>
+        <v>-0.009157509157509115</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.0251945525291829</v>
+        <v>-0.04377431906614793</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0005893909626718763</v>
+        <v>-0.001021400778210113</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01763474620617483</v>
+        <v>-0.01517530088958657</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.02564643799472296</v>
+        <v>-0.02684824902723737</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.01576172904586195</v>
+        <v>-0.01797642436149316</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.008645229309435986</v>
+        <v>-0.01644575355915567</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0002431906614785984</v>
+        <v>-0.0001055408970976224</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.007801792303637356</v>
+        <v>-0.007357859531772626</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.005154639175257714</v>
+        <v>-0.00706605222734249</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.002237354085603138</v>
+        <v>-0.002603143418467613</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.004715127701375221</v>
+        <v>-0.01114931237721024</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.008909370199692745</v>
+        <v>-0.005494505494505553</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.02002945508100142</v>
+        <v>-0.006554019457245231</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0006809338521400754</v>
+        <v>-0.0003404669260700377</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.001528905876732023</v>
+        <v>-0.0006688963210703003</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.004123711340206171</v>
+        <v>-0.002111984282907664</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.0003663003663004205</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.0008349705304518396</v>
+        <v>-0.002996070726915567</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.005494505494505542</v>
+        <v>-0.008602150537634367</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0.002508960573476682</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.001159725882973139</v>
+        <v>-0.004616895874263294</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.00549450549450553</v>
+        <v>-0.01193516699410611</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.006872852233676952</v>
+        <v>-0.009052851909994752</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.001129666011787822</v>
+        <v>-0.00191552062868372</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.007782898105478708</v>
+        <v>-0.007117255504352238</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.008038914490527372</v>
+        <v>-0.005808477237048626</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.006167633104902526</v>
+        <v>-0.002341137123745851</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002558705138104161</v>
+        <v>-0.001345016853757352</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.003514864441770113</v>
+        <v>-0.00423249933537958</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.00617559003023061</v>
+        <v>-0.001150818737944842</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001105108055009829</v>
+        <v>-0.0008506348044114709</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.004126427805346274</v>
+        <v>-0.005100715550853655</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001297121649552896</v>
+        <v>-0.0007003722634542574</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0001013628722925819</v>
+        <v>-0.0001791686574295459</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.002741643172179958</v>
+        <v>-0.004622592448267432</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001349118904716318</v>
+        <v>-0.000881596260075762</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001577763457072356</v>
+        <v>-0.003254399686698231</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0007745923692014823</v>
+        <v>0.0004083234424122062</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.000846869746622636</v>
+        <v>-0.001336390695590669</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006838861598167407</v>
+        <v>-0.001852043889601923</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.001173315378711892</v>
+        <v>-0.008064739316133445</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00274006835800551</v>
+        <v>0.002542169261153757</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0004507911108166673</v>
+        <v>-0.002404501953708796</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0001279496982475147</v>
+        <v>-0.001598923823012194</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.004046258570564731</v>
+        <v>-0.002158158463710236</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0003301607371308135</v>
+        <v>-0.00446473461626265</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-3.957783641160839e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.003043975018156239</v>
+        <v>-0.002126199771052822</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001443298839266846</v>
+        <v>-0.005952607390580549</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0004697566349463167</v>
+        <v>-0.001715127449885664</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0008785214464662905</v>
+        <v>-0.00204565836059114</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0004271608308875879</v>
+        <v>-0.0006399144281495016</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0003861445948125319</v>
+        <v>-0.0008344397575325568</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.001557543270817963</v>
+        <v>-0.002521106370664117</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.003711532631640055</v>
+        <v>-0.008412568881155453</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.002643605819273323</v>
+        <v>-0.003795141990186541</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.002388779633488852</v>
+        <v>-0.01188856012984092</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0004444527546548144</v>
+        <v>-0.001100625058491497</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0004369620422277537</v>
+        <v>-0.0003990884740606604</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.004623800352813612</v>
+        <v>-0.003575368596101317</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.004357051873189985</v>
+        <v>-0.002241550527307071</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0002311926806312481</v>
+        <v>-0.0003351653996301413</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0006703307992602881</v>
+        <v>-0.0004506285397374521</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001478399558074128</v>
+        <v>-0.0007342181109423502</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.002156240442483837</v>
+        <v>-0.003685163487333198</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0001314982146536497</v>
+        <v>-0.0008574836414949133</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0004777640664514416</v>
+        <v>-0.0007945049550351246</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.399199663430387e-05</v>
+        <v>-0.002345892712068351</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0001448936407970142</v>
+        <v>-0.002192458725637947</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.003545694965714902</v>
+        <v>-0.008059392537675233</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.01012813079452575</v>
+        <v>-0.01089629673910878</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0003184713375795984</v>
+        <v>-0.0003269482726274447</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001842323076147415</v>
+        <v>-0.003725768848262903</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0006437915211286533</v>
+        <v>-0.0005335398038659345</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0007372904986937823</v>
+        <v>-0.002590659489040201</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.009023585627561332</v>
+        <v>-0.003470895614726002</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.004121872006453461</v>
+        <v>-0.003373480559049691</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.009627914630294929</v>
+        <v>-0.00850719021702089</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0002160055925965465</v>
+        <v>-0.0008759325855171862</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0001549076340412431</v>
+        <v>-0.0004474500826927713</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.003126349846653626</v>
+        <v>-0.0008955353610861749</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.00981977514837346</v>
+        <v>-0.006717173583179697</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.005082953444926453</v>
+        <v>-0.007601576610793156</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0006877493866018769</v>
+        <v>-0.0009551042157178502</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.003715122780168126</v>
+        <v>-0.0004665736032126055</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.008190235265011538</v>
+        <v>-0.007775998901587129</v>
       </c>
       <c r="BL6" t="n">
-        <v>-3.33066907387547e-17</v>
+        <v>-0.0004664203396303995</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.001529721518413324</v>
+        <v>0.0001910371073083922</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.00750224961303296</v>
+        <v>-0.005366215343479424</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.007524823870959643</v>
+        <v>-0.005038312124546027</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.004863651479880243</v>
+        <v>-0.004801976891738502</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-3.840245775729445e-05</v>
+        <v>-3.683693516701448e-05</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001060723829050608</v>
+        <v>-0.003168781790361402</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.00158564419239173</v>
+        <v>-0.001725110493018495</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0005410511514825578</v>
+        <v>-0.0009539298392164386</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.001567493304446418</v>
+        <v>-0.007051012316108102</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.002343992476492232</v>
+        <v>-0.002107180947630677</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.005407499607724265</v>
+        <v>-0.004586799723509769</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0002559552248993568</v>
+        <v>-3.583373148591251e-05</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.000294886304199346</v>
+        <v>-0.0002820014722916348</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0001420451904718872</v>
+        <v>-0.0002770004322799613</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0003139717425432009</v>
+        <v>-0.0001448575567359001</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.002794428533386956</v>
+        <v>-0.002072914812237306</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0.0001581271958016994</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.227897838901038e-05</v>
+        <v>-0.0006533904319839829</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.00242806467448965</v>
+        <v>-0.005057504689587516</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.005126021710874437</v>
+        <v>-0.0008787268312145158</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.000621118012422417</v>
+        <v>-0.000507672051450811</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.004905157594534551</v>
+        <v>-0.0006976988922165195</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.006513761387016689</v>
+        <v>-0.003121547453998175</v>
       </c>
       <c r="CK6" t="n">
-        <v>-3.477733907153446e-05</v>
+        <v>-0.002054945825995505</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001295276541053325</v>
+        <v>8.450034965663545e-05</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.000682166832316572</v>
+        <v>0.001746799652669934</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0004112598053956751</v>
+        <v>-0.0004333487901012012</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007458177561270041</v>
+        <v>0.0007208976678480472</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001042711160482651</v>
+        <v>-0.002155606868725957</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.590074284620323e-05</v>
+        <v>0.0009529872694077623</v>
       </c>
       <c r="I7" t="n">
-        <v>5.307855626327518e-05</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002228821742812892</v>
+        <v>-0.0006794997306330708</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008458417278790709</v>
+        <v>0.01525095685279532</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004075403174860381</v>
+        <v>0.008439087954633467</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001556668627275054</v>
+        <v>0.002340248793604527</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00132126286997909</v>
+        <v>0.002608832759188018</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001695048610499644</v>
+        <v>0.000929249700860285</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007529863978908553</v>
+        <v>0.01085899863514002</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0105150099760727</v>
+        <v>0.006815224664799629</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001852475189902042</v>
+        <v>0.0003737701058266818</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002291016649606931</v>
+        <v>0.0007257740760000297</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00052404995049532</v>
+        <v>0.001565448048597312</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002489916474799597</v>
+        <v>0.001072427816807186</v>
       </c>
       <c r="V7" t="n">
-        <v>2.455795677800965e-05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002262555277108669</v>
+        <v>-0.0009753904428458915</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002662639766524455</v>
+        <v>-0.002056657212968133</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001573099556763902</v>
+        <v>0.0001992075662490322</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001334463231642435</v>
+        <v>-0.0008146487617873232</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002123859874661843</v>
+        <v>0.000973704033303674</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.467107651970561e-05</v>
+        <v>-0.0001589275610753394</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.003340048566404435</v>
+        <v>0.0003054328329032186</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.001721201732125538</v>
+        <v>-0.0007680227247131189</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001522779616501174</v>
+        <v>-0.0007171045415420574</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.001392714775207227</v>
+        <v>-0.002150844822292669</v>
       </c>
       <c r="AG7" t="n">
-        <v>-2.520264734519606e-05</v>
+        <v>5.551115123125783e-18</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.185613852471297e-05</v>
+        <v>-9.74017658012971e-05</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.001371415446840207</v>
+        <v>-0.001357131481355084</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.0004247825039633668</v>
+        <v>1.328688185139317e-05</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0001923820935850584</v>
+        <v>-0.0001713676364685224</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0002756193270471718</v>
+        <v>0.0001046572475144059</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001075575631247794</v>
+        <v>0.000131946458152149</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0001346065529636953</v>
+        <v>0.000231782141090936</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.271481286240331e-05</v>
+        <v>-0.0001473356847245533</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0004104297440850058</v>
+        <v>0.001440962413397462</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0008396732065197255</v>
+        <v>0.0002447743371443212</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0009396664359760053</v>
+        <v>2.78782020207813e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0003112822815526772</v>
+        <v>-0.0003927223574095418</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.003653597406266767</v>
+        <v>-0.008201041325805718</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.001558428252820554</v>
+        <v>0.0002754394259701254</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.001271708158740253</v>
+        <v>-0.0007891034080860726</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.0003042612762789776</v>
+        <v>-2.653927813162649e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001021473448947463</v>
+        <v>-0.001163087814492142</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.00399176392965217</v>
+        <v>0.0005542722136259948</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.001042071088154034</v>
+        <v>0.0006420103194297033</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.00145081786551054</v>
+        <v>-0.003619092183309919</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0002819728345122785</v>
+        <v>-0.0003693653219984772</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0001500467131402505</v>
+        <v>-7.886790188880721e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.0003983312870194655</v>
+        <v>-0.00013120774849818</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.001740425769535248</v>
+        <v>-0.001964209334768063</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.002600403358860697</v>
+        <v>-0.0005846688981984039</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.000211589652583466</v>
+        <v>4.777830864786669e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-6.636809824588362e-05</v>
+        <v>0.0007405257439873913</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0006950606329487796</v>
+        <v>-0.0007456392200162476</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0001215953307393047</v>
+        <v>-0.0001846965699208392</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.001119290245404092</v>
+        <v>0.000729809559930561</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.00389982163797436</v>
+        <v>-0.0009302908268495891</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.004038546404713106</v>
+        <v>-0.00157196171734944</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.001661245341115858</v>
+        <v>-0.000517222080304075</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.388915432393613e-05</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0003317776188364041</v>
+        <v>-0.001276555626605258</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.0007475279974338333</v>
+        <v>-0.0008546644361718481</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0003430105814397622</v>
+        <v>-0.0001792114695340297</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0009044997572967062</v>
+        <v>-0.002338557652802309</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.00043703863056061</v>
+        <v>0.0002936434712679237</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0.0008365768855524925</v>
+        <v>-0.001647458257402507</v>
       </c>
       <c r="BX7" t="n">
-        <v>-7.907221929362996e-05</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-2.560163850484076e-05</v>
+        <v>0.0001588607025368005</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0003423858519399914</v>
+        <v>-2.635740643118778e-05</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0001746738870025799</v>
+        <v>0.000342508438250344</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.0008649686787644161</v>
+        <v>-0.0007052658251465394</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.000290521062895599</v>
+        <v>2.431906614785984e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0004745167692913443</v>
+        <v>-0.0006127401821172107</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.001228894050138291</v>
+        <v>0.0006291251993905123</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.000223312019298294</v>
+        <v>-0.0001582557099600312</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.001172556465513541</v>
+        <v>0.001548502387362466</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0005094674089285711</v>
+        <v>-9.727626459144489e-05</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0009357373674128866</v>
+        <v>-0.0001235328710166572</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003730800731943762</v>
+        <v>0.004753268742752493</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002942128996390769</v>
+        <v>0.004805793285056014</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003767722070667337</v>
+        <v>0.0004941520649004161</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001621130876386676</v>
+        <v>0.002080484799378851</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001734819041231755</v>
+        <v>1.762333204024526e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001932308918603587</v>
+        <v>0.002238024212056838</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000353441542544708</v>
+        <v>0.0002898349234670055</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00644591618384994</v>
+        <v>0.001090779547232068</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01545164457535595</v>
+        <v>0.02313941745242931</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0084164239559338</v>
+        <v>0.03200243228109474</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004037449873746729</v>
+        <v>0.003589629831865843</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002267433770114843</v>
+        <v>0.005116892745861142</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003860902586134399</v>
+        <v>0.002401543615695676</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01182038507551871</v>
+        <v>0.01358955616327001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01974192324931905</v>
+        <v>0.0269623233908948</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004839523990129069</v>
+        <v>0.004310769533323164</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00442287911479273</v>
+        <v>0.003534617337943172</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002271562298488605</v>
+        <v>0.005277682133959832</v>
       </c>
       <c r="U8" t="n">
-        <v>0.005946274452844888</v>
+        <v>0.004332468773462586</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002677728374642363</v>
+        <v>0.0003010718336755481</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002937577015918041</v>
+        <v>0.006575820927614853</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003559483994266555</v>
+        <v>0.0003163916105070469</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00285591670673376</v>
+        <v>0.001768089048055738</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.000846411534494354</v>
+        <v>0.0005079289240779661</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004193544880956889</v>
+        <v>0.002207636582993228</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0002406504210822252</v>
+        <v>0.0004132091686016554</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.004374179037894379</v>
+        <v>0.001954432269521428</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002372879565667477</v>
+        <v>0.001473202827428319</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.003678807763882163</v>
+        <v>0.0007652485308864115</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.509377340069284e-05</v>
+        <v>0.0006988267603372511</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0001037607605175683</v>
+        <v>0.0002513732097444848</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0006626616093792642</v>
+        <v>0.0001187335092348252</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.003409427567912809</v>
+        <v>0.001362249929288362</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.004542686525959211</v>
+        <v>0.001431734534393242</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0004022417258974509</v>
+        <v>7.907221929362996e-05</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0004457559319735016</v>
+        <v>0.0005819345102194644</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002315249960836879</v>
+        <v>0.0007666024974855661</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.003555178980065588</v>
+        <v>0.002669089027502522</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0005505476201427356</v>
+        <v>0.0003433930502103583</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002027312165561021</v>
+        <v>0.00263892339787824</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.001639945638224685</v>
+        <v>0.001379833329735061</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.00195514909810813</v>
+        <v>0.002120796447160303</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.005450253260296558</v>
+        <v>0.001040809022519251</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0001631897802737093</v>
+        <v>0.0001182538499071128</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.003830112184477186</v>
+        <v>0.0008190811837375355</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.002884420634759882</v>
+        <v>0.002016417176799096</v>
       </c>
       <c r="AX8" t="n">
-        <v>-1.194457716197084e-05</v>
+        <v>7.166746297181115e-05</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.002310308138574716</v>
+        <v>0.0002906450375987635</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001415985802175818</v>
+        <v>0.003117125362776407</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.003106286161802344</v>
+        <v>0.004541467864159399</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.01381971067102976</v>
+        <v>-0.0009598162415989819</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0006774587419748456</v>
+        <v>3.681885125184081e-05</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0003346634616835875</v>
+        <v>5.181508803580315e-05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0006640680366869656</v>
+        <v>-1.326963906580769e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.002305807296617887</v>
+        <v>0.004622915552720519</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.000155241463050948</v>
+        <v>0.002156635953240291</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0001594192037293163</v>
+        <v>0.000301310724305695</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001276461108360252</v>
+        <v>0.001787067109374427</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.00153706218012089</v>
+        <v>0.0007047490725834798</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.001239020645012318</v>
+        <v>0.0004371972113908134</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.004675458737699085</v>
+        <v>0.003043944409194788</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0.0006476187051222271</v>
+        <v>0.005349331060204604</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0005250233659559984</v>
+        <v>0.003178492670719638</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001118660144665526</v>
+        <v>0.002304099976386776</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.890839822833115e-05</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.002221930376460651</v>
+        <v>0.002522891188660081</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0001052797203242972</v>
+        <v>0.0002181958491160818</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0006665498040002438</v>
+        <v>0.000597152777989124</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002374365188944083</v>
+        <v>0.0009168929745622888</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0009573624682084808</v>
+        <v>0.003633980331997197</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001075927273097904</v>
+        <v>0.001405577856944851</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.000431954125111092</v>
+        <v>0.0005799742128593771</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0006181348000596193</v>
+        <v>0.00012080270062583</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0004837917874167153</v>
+        <v>0.000516697500914981</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.000625605351855904</v>
+        <v>0.0004232057672471645</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001025323208233997</v>
+        <v>0.0009654419077327836</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0009767140169446519</v>
+        <v>0.002961442879734949</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0003446145724422505</v>
+        <v>0.001430550658144506</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001126616856980464</v>
+        <v>0.0002371728125224792</v>
       </c>
       <c r="CI8" t="n">
-        <v>5.144497417392536e-05</v>
+        <v>0.002427503114155638</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.00164034191933066</v>
+        <v>0.003659875332184839</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001780697068738152</v>
+        <v>0.004409905850210611</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01046572475143898</v>
+        <v>0.006384092098377836</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009921414538310424</v>
+        <v>0.008742632612966561</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006596306068601565</v>
+        <v>0.002930402930402976</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01186083289404321</v>
+        <v>0.003271767810026382</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004134241245136172</v>
+        <v>0.009868073878627971</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004076620825147348</v>
+        <v>0.009973614775725604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005836575875486361</v>
+        <v>0.0006385068762278622</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01035992217898829</v>
+        <v>0.01110019646365419</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0326325848064978</v>
+        <v>0.05398948877209744</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03024366937410411</v>
+        <v>0.04515050167224077</v>
       </c>
       <c r="M9" t="n">
-        <v>0.006802721088435315</v>
+        <v>0.00543535620052773</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004815175097276247</v>
+        <v>0.008126649076517145</v>
       </c>
       <c r="O9" t="n">
-        <v>0.005171503957783608</v>
+        <v>0.006437994722955154</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02258222876779581</v>
+        <v>0.0203693931398417</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0385138670852956</v>
+        <v>0.0341137123745819</v>
       </c>
       <c r="R9" t="n">
-        <v>0.007023575638506885</v>
+        <v>0.009528487229862447</v>
       </c>
       <c r="S9" t="n">
-        <v>0.005785970302099352</v>
+        <v>0.0108811040339703</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01369661266568489</v>
+        <v>0.01139841688654354</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01465201465201459</v>
+        <v>0.01608280254777074</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001313229571984431</v>
+        <v>0.001915520628683665</v>
       </c>
       <c r="W9" t="n">
-        <v>0.008365758754863784</v>
+        <v>0.008843537414966008</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009728622631848472</v>
+        <v>0.0047619047619048</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.007538910505836549</v>
+        <v>0.00311345646437996</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001741424802110792</v>
+        <v>0.004045058883768604</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004864311315924241</v>
+        <v>0.00440348182283673</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0003690036900368621</v>
+        <v>0.0008372579801151803</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01119832548403972</v>
+        <v>0.01049667178699439</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.009125656951743843</v>
+        <v>0.003891449052739415</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.004557091653865886</v>
+        <v>0.005376344086021567</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.003440038222646857</v>
+        <v>0.00200527704485487</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0005277044854881119</v>
+        <v>0.0006852925672114152</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0008970976253297902</v>
+        <v>0.001370585134422819</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01016536964980541</v>
+        <v>0.004511677282377946</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01658986175115211</v>
+        <v>0.003487816531294752</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0006802721088434826</v>
+        <v>0.0005232862375720182</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007380073800737797</v>
+        <v>0.003123399897593493</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.007936507936507964</v>
+        <v>0.004217185028993176</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.01352126134734825</v>
+        <v>0.006528662420382192</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002869649805447461</v>
+        <v>0.001255886970172715</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.008608949416342382</v>
+        <v>0.009216589861751168</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.003976975405546779</v>
+        <v>0.004485488126649095</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.008434370057986274</v>
+        <v>0.003268318397469727</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.009314495028780701</v>
+        <v>0.006331763474620633</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.001605058365758727</v>
+        <v>0.01003584229390683</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.006760700389105034</v>
+        <v>0.007757255936675467</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.01585603112840461</v>
+        <v>0.007757255936675455</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.000289715113471789</v>
+        <v>0.0006802721088435826</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.005956773853452802</v>
+        <v>0.009656992084432704</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.003732809430255424</v>
+        <v>0.00674097664543527</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.007740086000955515</v>
+        <v>0.008276225619399113</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.02250358337314855</v>
+        <v>0.01600573339703769</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001159725882973095</v>
+        <v>0.001070038910505833</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001963672066764843</v>
+        <v>0.0004777830864787225</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.003821656050955435</v>
+        <v>0.003534609720176718</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01060678451982794</v>
+        <v>0.01094123268036307</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.004813359528487248</v>
+        <v>0.00743278861360046</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0005271481286241219</v>
+        <v>0.00194572452636973</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.007782101167315147</v>
+        <v>0.009182058047493424</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.004533473906167618</v>
+        <v>0.01043753294675809</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.003043691703485507</v>
+        <v>0.00148112756808404</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.005496108949416323</v>
+        <v>0.01361477572559367</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.002798232695139902</v>
+        <v>0.01012900143334922</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01389297987236138</v>
+        <v>0.006306736741519314</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.004564755838641232</v>
+        <v>0.02298301486199577</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0002638522427440559</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.00500736377025035</v>
+        <v>0.007377919320594506</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.008704883227176241</v>
+        <v>0.003874734607218688</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002603143418467602</v>
+        <v>0.004168865435356195</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.004511677282377957</v>
+        <v>0.007229551451187343</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.005201698513800456</v>
+        <v>0.009857670005271536</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01119957537154992</v>
+        <v>0.006475583864118927</v>
       </c>
       <c r="BX9" t="n">
-        <v>5.120327700973704e-05</v>
+        <v>0.0001055408970976224</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.001620029455080996</v>
+        <v>0.001331285202252996</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002304147465437845</v>
+        <v>0.0003927344133529687</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0004749340369393007</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002108592514496532</v>
+        <v>0.001477572559366758</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.01293774319066143</v>
+        <v>0.007643647865050118</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.000369003690036851</v>
+        <v>4.863813229571967e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001517530088958596</v>
+        <v>0.00194572452636973</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.003184713375796189</v>
+        <v>0.0150743099787686</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.004989384288747368</v>
+        <v>0.006740976645435282</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002503681885125175</v>
+        <v>0.0003822264691829669</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.006104033970276024</v>
+        <v>0.004485488126649073</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.00605095541401276</v>
+        <v>0.0131634819532909</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.005732484076433153</v>
+        <v>0.006774668630338709</v>
       </c>
     </row>
   </sheetData>
